--- a/artfynd/A 42512-2019 artfynd.xlsx
+++ b/artfynd/A 42512-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121461375</v>
       </c>
       <c r="B2" t="n">
-        <v>98102</v>
+        <v>98115</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>121461364</v>
       </c>
       <c r="B3" t="n">
-        <v>97035</v>
+        <v>97048</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 42512-2019 artfynd.xlsx
+++ b/artfynd/A 42512-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121461375</v>
+        <v>121461364</v>
       </c>
       <c r="B2" t="n">
-        <v>98115</v>
+        <v>97049</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121461364</v>
+        <v>121461375</v>
       </c>
       <c r="B3" t="n">
-        <v>97048</v>
+        <v>98116</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>

--- a/artfynd/A 42512-2019 artfynd.xlsx
+++ b/artfynd/A 42512-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121461364</v>
+        <v>121461375</v>
       </c>
       <c r="B2" t="n">
-        <v>97049</v>
+        <v>98119</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121461375</v>
+        <v>121461364</v>
       </c>
       <c r="B3" t="n">
-        <v>98116</v>
+        <v>97052</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>

--- a/artfynd/A 42512-2019 artfynd.xlsx
+++ b/artfynd/A 42512-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121461375</v>
       </c>
       <c r="B2" t="n">
-        <v>98119</v>
+        <v>98125</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>121461364</v>
       </c>
       <c r="B3" t="n">
-        <v>97052</v>
+        <v>97058</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 42512-2019 artfynd.xlsx
+++ b/artfynd/A 42512-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121461375</v>
       </c>
       <c r="B2" t="n">
-        <v>98125</v>
+        <v>98126</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>121461364</v>
       </c>
       <c r="B3" t="n">
-        <v>97058</v>
+        <v>97059</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 42512-2019 artfynd.xlsx
+++ b/artfynd/A 42512-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121461375</v>
+        <v>121461364</v>
       </c>
       <c r="B2" t="n">
-        <v>98126</v>
+        <v>97059</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121461364</v>
+        <v>121461375</v>
       </c>
       <c r="B3" t="n">
-        <v>97059</v>
+        <v>98126</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>

--- a/artfynd/A 42512-2019 artfynd.xlsx
+++ b/artfynd/A 42512-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121461364</v>
+        <v>121461375</v>
       </c>
       <c r="B2" t="n">
-        <v>97059</v>
+        <v>98134</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121461375</v>
+        <v>121461364</v>
       </c>
       <c r="B3" t="n">
-        <v>98126</v>
+        <v>97067</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>

--- a/artfynd/A 42512-2019 artfynd.xlsx
+++ b/artfynd/A 42512-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121461375</v>
+        <v>121461364</v>
       </c>
       <c r="B2" t="n">
-        <v>98134</v>
+        <v>97067</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121461364</v>
+        <v>121461375</v>
       </c>
       <c r="B3" t="n">
-        <v>97067</v>
+        <v>98134</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
